--- a/endorsements2.xlsx
+++ b/endorsements2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robschoen/Dropbox/CC/JVS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72621CD6-3F0E-574E-BBBB-FFD963753305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E9B32E-579E-F241-BADA-C9629E4CA02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5840" yWindow="3440" windowWidth="28160" windowHeight="17180" xr2:uid="{75493C79-CDBF-064E-8FA7-03F55FC4DAC2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="346">
   <si>
     <t>Nancy Adler</t>
   </si>
@@ -588,13 +588,499 @@
   </si>
   <si>
     <t>Former Select Board</t>
+  </si>
+  <si>
+    <t> Pat Ahlin</t>
+  </si>
+  <si>
+    <t> Martina Albright</t>
+  </si>
+  <si>
+    <t> Saralynn Allaire</t>
+  </si>
+  <si>
+    <t> Pamela Allara</t>
+  </si>
+  <si>
+    <t> Scott Andersen</t>
+  </si>
+  <si>
+    <t> Rosemary Ashby</t>
+  </si>
+  <si>
+    <t> John Bassett</t>
+  </si>
+  <si>
+    <t> Jim Batchelor</t>
+  </si>
+  <si>
+    <t> Clara Batchelor</t>
+  </si>
+  <si>
+    <t> Jerry Berger</t>
+  </si>
+  <si>
+    <t> Susan Berger</t>
+  </si>
+  <si>
+    <t> Eileen Berger</t>
+  </si>
+  <si>
+    <t> Michael Berger</t>
+  </si>
+  <si>
+    <t> Ben Binbaum</t>
+  </si>
+  <si>
+    <t> Peter Bleyleben</t>
+  </si>
+  <si>
+    <t> Sara Salvo Blood</t>
+  </si>
+  <si>
+    <t> Roger Blood</t>
+  </si>
+  <si>
+    <t> Sam Botsford</t>
+  </si>
+  <si>
+    <t> Edie Brickman</t>
+  </si>
+  <si>
+    <t> Pauline Hо Bупum</t>
+  </si>
+  <si>
+    <t> Narcissa Campion</t>
+  </si>
+  <si>
+    <t> Peggy Campion</t>
+  </si>
+  <si>
+    <t> Tracy Clark</t>
+  </si>
+  <si>
+    <t> Abby Coffin</t>
+  </si>
+  <si>
+    <t> Susan F Cohen</t>
+  </si>
+  <si>
+    <t> Debby K Cohen</t>
+  </si>
+  <si>
+    <t> George Cole</t>
+  </si>
+  <si>
+    <t> Susan Helms Daley</t>
+  </si>
+  <si>
+    <t> Susan Dechter</t>
+  </si>
+  <si>
+    <t> John Dempsey</t>
+  </si>
+  <si>
+    <t> Marie desJardins</t>
+  </si>
+  <si>
+    <t> Murray Dewart</t>
+  </si>
+  <si>
+    <t> Mary Dewart</t>
+  </si>
+  <si>
+    <t> Dennis Dewitt</t>
+  </si>
+  <si>
+    <t> John Doggett</t>
+  </si>
+  <si>
+    <t> David Eisenberg</t>
+  </si>
+  <si>
+    <t> Elton Elperin</t>
+  </si>
+  <si>
+    <t> Tom Elwertowski</t>
+  </si>
+  <si>
+    <t> Elizabeth Erdman</t>
+  </si>
+  <si>
+    <t> Sarah Ericsson</t>
+  </si>
+  <si>
+    <t> Susan Erickson</t>
+  </si>
+  <si>
+    <t> Anne Farrington</t>
+  </si>
+  <si>
+    <t> Chuck Farrington</t>
+  </si>
+  <si>
+    <t> Jonathan Fine</t>
+  </si>
+  <si>
+    <t> Marcia Fisch</t>
+  </si>
+  <si>
+    <t> Julian Fisher</t>
+  </si>
+  <si>
+    <t> Dale Flecker</t>
+  </si>
+  <si>
+    <t> Marion Freedman-Gurspan</t>
+  </si>
+  <si>
+    <t> Anita Fritze</t>
+  </si>
+  <si>
+    <t> David Marc Goldstein</t>
+  </si>
+  <si>
+    <t> Ellen Golde</t>
+  </si>
+  <si>
+    <t> Bambi Good</t>
+  </si>
+  <si>
+    <t> Ellen Goodman</t>
+  </si>
+  <si>
+    <t> Rhoda Goodwin</t>
+  </si>
+  <si>
+    <t> Mark Gray</t>
+  </si>
+  <si>
+    <t> Nathan Gunner</t>
+  </si>
+  <si>
+    <t> Sally Guy</t>
+  </si>
+  <si>
+    <t> Benedicte Hallowell</t>
+  </si>
+  <si>
+    <t> Rory Hallowell</t>
+  </si>
+  <si>
+    <t> Casey Hatchett</t>
+  </si>
+  <si>
+    <t> Debbie Hatzieleftheriadis</t>
+  </si>
+  <si>
+    <t> Gerard Hayes</t>
+  </si>
+  <si>
+    <t> Barbara Hebert</t>
+  </si>
+  <si>
+    <t> John Hebert</t>
+  </si>
+  <si>
+    <t> Robin Hennessey</t>
+  </si>
+  <si>
+    <t> Carol Hillman</t>
+  </si>
+  <si>
+    <t> Fran Hoy</t>
+  </si>
+  <si>
+    <t> Richard Mazandi Iseke</t>
+  </si>
+  <si>
+    <t> Cerise Jacobs</t>
+  </si>
+  <si>
+    <t> Nicholas Johnson</t>
+  </si>
+  <si>
+    <t> Joyce Jozwicki</t>
+  </si>
+  <si>
+    <t> Barr Jozwicki</t>
+  </si>
+  <si>
+    <t> Janice Kahn</t>
+  </si>
+  <si>
+    <t> Ruth Kaplan</t>
+  </si>
+  <si>
+    <t> Priscilla Karnovsky</t>
+  </si>
+  <si>
+    <t> Kitty Kaufman</t>
+  </si>
+  <si>
+    <t> Janet Kawada</t>
+  </si>
+  <si>
+    <t> David King</t>
+  </si>
+  <si>
+    <t> Kristine Knauf</t>
+  </si>
+  <si>
+    <t> Geri Lambert</t>
+  </si>
+  <si>
+    <t> Jonathan Lau</t>
+  </si>
+  <si>
+    <t> Marian Lazar</t>
+  </si>
+  <si>
+    <t> Gerald Lazar</t>
+  </si>
+  <si>
+    <t> Frederick Lebow</t>
+  </si>
+  <si>
+    <t> Stephen Ledbetter</t>
+  </si>
+  <si>
+    <t> David Lescohier</t>
+  </si>
+  <si>
+    <t> Carol Levin</t>
+  </si>
+  <si>
+    <t> Bruce Levin</t>
+  </si>
+  <si>
+    <t> Fred Levitan</t>
+  </si>
+  <si>
+    <t> Alan Leviton</t>
+  </si>
+  <si>
+    <t> Nancy Lew</t>
+  </si>
+  <si>
+    <t> Ken Lewis</t>
+  </si>
+  <si>
+    <t> Karen Livingston</t>
+  </si>
+  <si>
+    <t> Pam Lodish</t>
+  </si>
+  <si>
+    <t> Mark Lowenstein</t>
+  </si>
+  <si>
+    <t> Richard Mai</t>
+  </si>
+  <si>
+    <t> Carol Macbain</t>
+  </si>
+  <si>
+    <t> Lucy Mack</t>
+  </si>
+  <si>
+    <t> Linda Mancini</t>
+  </si>
+  <si>
+    <t> Jon Margolis</t>
+  </si>
+  <si>
+    <t> Hugh Mattison</t>
+  </si>
+  <si>
+    <t> Arlene Mattison</t>
+  </si>
+  <si>
+    <t> Michael Maynard</t>
+  </si>
+  <si>
+    <t> Chris McArdle</t>
+  </si>
+  <si>
+    <t> Colin McArdle</t>
+  </si>
+  <si>
+    <t> Diana McClure</t>
+  </si>
+  <si>
+    <t> John McCullough</t>
+  </si>
+  <si>
+    <t> Eric McNulty</t>
+  </si>
+  <si>
+    <t> Steve Mead</t>
+  </si>
+  <si>
+    <t> Letitia Mead</t>
+  </si>
+  <si>
+    <t> Randolph Meiklejohn</t>
+  </si>
+  <si>
+    <t> Robert Melzer</t>
+  </si>
+  <si>
+    <t> Dr Keith Merlin</t>
+  </si>
+  <si>
+    <t> Judy Meyer</t>
+  </si>
+  <si>
+    <t> Jessica Milhem</t>
+  </si>
+  <si>
+    <t> Paul Hart Miller</t>
+  </si>
+  <si>
+    <t> Peggy Morrison</t>
+  </si>
+  <si>
+    <t> Tom Mullin</t>
+  </si>
+  <si>
+    <t> Terry Murphy</t>
+  </si>
+  <si>
+    <t> Kendra O'Donnell</t>
+  </si>
+  <si>
+    <t> Larry Onie</t>
+  </si>
+  <si>
+    <t> John Parla</t>
+  </si>
+  <si>
+    <t> Linda Olson Pehlke</t>
+  </si>
+  <si>
+    <t> Danna Perry</t>
+  </si>
+  <si>
+    <t> Alisa Plazonja</t>
+  </si>
+  <si>
+    <t> Betsy Pollock</t>
+  </si>
+  <si>
+    <t> Susan Podziba</t>
+  </si>
+  <si>
+    <t> Luisa Raposo</t>
+  </si>
+  <si>
+    <t> Judy Reece</t>
+  </si>
+  <si>
+    <t> Gleeson Rebello</t>
+  </si>
+  <si>
+    <t> Peter Richardson</t>
+  </si>
+  <si>
+    <t> Pam Roberts</t>
+  </si>
+  <si>
+    <t> Rosemarie Roque</t>
+  </si>
+  <si>
+    <t> Barry Rosen</t>
+  </si>
+  <si>
+    <t> A. Joseph Ross</t>
+  </si>
+  <si>
+    <t> Jeffrey Ross</t>
+  </si>
+  <si>
+    <t> Christine Rossell</t>
+  </si>
+  <si>
+    <t> Stuart Rubinow</t>
+  </si>
+  <si>
+    <t> Bonnie Sashin</t>
+  </si>
+  <si>
+    <t> Cheryl Schaffer</t>
+  </si>
+  <si>
+    <t> Jill Schiff</t>
+  </si>
+  <si>
+    <t> Cathleen Schoen</t>
+  </si>
+  <si>
+    <t> Robert Schoen</t>
+  </si>
+  <si>
+    <t> John Seay</t>
+  </si>
+  <si>
+    <t> Judy Selwyn</t>
+  </si>
+  <si>
+    <t> Lee Selwyn</t>
+  </si>
+  <si>
+    <t> Ronnie Shapiro</t>
+  </si>
+  <si>
+    <t> Francis Shedd-Fisher</t>
+  </si>
+  <si>
+    <t> Barbara Sherman</t>
+  </si>
+  <si>
+    <t> John Sherman</t>
+  </si>
+  <si>
+    <t> Ellen Shoner</t>
+  </si>
+  <si>
+    <t> John Shreffler</t>
+  </si>
+  <si>
+    <t> Felina Silver Robinson</t>
+  </si>
+  <si>
+    <t> Stanley Spiegel</t>
+  </si>
+  <si>
+    <t> Alexandra Spingarn</t>
+  </si>
+  <si>
+    <t> Molly Turlisch</t>
+  </si>
+  <si>
+    <t> Judith Vanderkay</t>
+  </si>
+  <si>
+    <t> Barbara VanScoyoc</t>
+  </si>
+  <si>
+    <t> Kathleen Vieweg</t>
+  </si>
+  <si>
+    <t> Donnie Wolosenko</t>
+  </si>
+  <si>
+    <t> Jerry Wolosenko</t>
+  </si>
+  <si>
+    <t> Mark Zarrillo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -625,6 +1111,25 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF3D3D3D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3D3D3D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -646,7 +1151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -654,6 +1159,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -988,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C33EE1-A309-1642-A501-03F53C3F9FA2}">
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:FQ163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -997,7 +1505,7 @@
     <col min="6" max="6" width="26.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:173">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1010,8 +1518,503 @@
       <c r="F1" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" t="s">
+        <v>184</v>
+      </c>
+      <c r="M1" t="s">
+        <v>185</v>
+      </c>
+      <c r="N1" t="s">
+        <v>186</v>
+      </c>
+      <c r="O1" t="s">
+        <v>187</v>
+      </c>
+      <c r="P1" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>189</v>
+      </c>
+      <c r="R1" t="s">
+        <v>190</v>
+      </c>
+      <c r="S1" t="s">
+        <v>191</v>
+      </c>
+      <c r="T1" t="s">
+        <v>192</v>
+      </c>
+      <c r="U1" t="s">
+        <v>193</v>
+      </c>
+      <c r="V1" t="s">
+        <v>194</v>
+      </c>
+      <c r="W1" t="s">
+        <v>195</v>
+      </c>
+      <c r="X1" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>203</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>205</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>212</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>213</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>215</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>216</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>218</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>221</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>222</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>223</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>224</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>225</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>227</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>228</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>235</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>236</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>237</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>238</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>239</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>240</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>241</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>242</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>243</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>244</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>245</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>246</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>247</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>248</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>249</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>250</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>251</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>253</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>254</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>255</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>256</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>257</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>258</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>259</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>260</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>261</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>262</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>263</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>264</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>265</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>266</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>267</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>268</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>269</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>270</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>271</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>272</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>273</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>274</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>275</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>276</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>277</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>278</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>279</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>280</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>281</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>282</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>283</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>284</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>285</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>286</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>287</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>288</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>289</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>290</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>291</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>292</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>293</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>294</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>295</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>296</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>297</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>298</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>299</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>300</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>301</v>
+      </c>
+      <c r="DZ1" t="s">
+        <v>302</v>
+      </c>
+      <c r="EA1" t="s">
+        <v>303</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>304</v>
+      </c>
+      <c r="EC1" t="s">
+        <v>305</v>
+      </c>
+      <c r="ED1" t="s">
+        <v>306</v>
+      </c>
+      <c r="EE1" t="s">
+        <v>307</v>
+      </c>
+      <c r="EF1" t="s">
+        <v>308</v>
+      </c>
+      <c r="EG1" t="s">
+        <v>309</v>
+      </c>
+      <c r="EH1" t="s">
+        <v>310</v>
+      </c>
+      <c r="EI1" t="s">
+        <v>311</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>312</v>
+      </c>
+      <c r="EK1" t="s">
+        <v>313</v>
+      </c>
+      <c r="EL1" t="s">
+        <v>314</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>315</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>316</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>317</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>318</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>319</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>320</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>321</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>322</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>323</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>324</v>
+      </c>
+      <c r="EW1" t="s">
+        <v>325</v>
+      </c>
+      <c r="EX1" t="s">
+        <v>326</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>327</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>328</v>
+      </c>
+      <c r="FA1" t="s">
+        <v>329</v>
+      </c>
+      <c r="FB1" t="s">
+        <v>330</v>
+      </c>
+      <c r="FC1" t="s">
+        <v>331</v>
+      </c>
+      <c r="FD1" t="s">
+        <v>332</v>
+      </c>
+      <c r="FE1" t="s">
+        <v>333</v>
+      </c>
+      <c r="FF1" t="s">
+        <v>334</v>
+      </c>
+      <c r="FG1" t="s">
+        <v>335</v>
+      </c>
+      <c r="FH1" t="s">
+        <v>336</v>
+      </c>
+      <c r="FI1" t="s">
+        <v>337</v>
+      </c>
+      <c r="FJ1" t="s">
+        <v>338</v>
+      </c>
+      <c r="FK1" t="s">
+        <v>339</v>
+      </c>
+      <c r="FL1" t="s">
+        <v>340</v>
+      </c>
+      <c r="FM1" t="s">
+        <v>341</v>
+      </c>
+      <c r="FN1" t="s">
+        <v>342</v>
+      </c>
+      <c r="FO1" t="s">
+        <v>343</v>
+      </c>
+      <c r="FP1" t="s">
+        <v>344</v>
+      </c>
+      <c r="FQ1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:173">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1024,8 +2027,14 @@
       <c r="F2" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" t="s">
+        <v>184</v>
+      </c>
+      <c r="J2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:173">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1038,8 +2047,15 @@
       <c r="F3" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:173">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +2069,15 @@
         <v>183</v>
       </c>
       <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:173">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1068,8 +2091,15 @@
         <v>183</v>
       </c>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" t="s">
+        <v>187</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:173">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1083,8 +2113,15 @@
         <v>183</v>
       </c>
       <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" t="s">
+        <v>188</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:173">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +2135,15 @@
         <v>180</v>
       </c>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:173">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1113,8 +2157,15 @@
         <v>180</v>
       </c>
       <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" t="s">
+        <v>190</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:173">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1128,8 +2179,15 @@
         <v>180</v>
       </c>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" t="s">
+        <v>191</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:173">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,8 +2201,15 @@
         <v>180</v>
       </c>
       <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:173">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1158,8 +2223,15 @@
         <v>180</v>
       </c>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:173">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1173,8 +2245,15 @@
         <v>181</v>
       </c>
       <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:173">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1188,8 +2267,15 @@
         <v>182</v>
       </c>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" t="s">
+        <v>195</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:173">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1203,8 +2289,15 @@
         <v>182</v>
       </c>
       <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" t="s">
+        <v>196</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:173">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,8 +2305,15 @@
         <v>14</v>
       </c>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" t="s">
+        <v>197</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:173">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1221,8 +2321,15 @@
         <v>15</v>
       </c>
       <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1230,8 +2337,15 @@
         <v>16</v>
       </c>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" t="s">
+        <v>199</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1239,8 +2353,15 @@
         <v>17</v>
       </c>
       <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" t="s">
+        <v>200</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1248,8 +2369,15 @@
         <v>18</v>
       </c>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" t="s">
+        <v>201</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1257,8 +2385,15 @@
         <v>19</v>
       </c>
       <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20" t="s">
+        <v>202</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1266,8 +2401,15 @@
         <v>20</v>
       </c>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" t="s">
+        <v>203</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -1275,8 +2417,15 @@
         <v>21</v>
       </c>
       <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" t="s">
+        <v>204</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="J22" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -1284,8 +2433,15 @@
         <v>22</v>
       </c>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" t="s">
+        <v>205</v>
+      </c>
+      <c r="I23" s="5"/>
+      <c r="J23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -1293,8 +2449,15 @@
         <v>157</v>
       </c>
       <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" t="s">
+        <v>206</v>
+      </c>
+      <c r="I24" s="5"/>
+      <c r="J24" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -1302,8 +2465,15 @@
         <v>23</v>
       </c>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" t="s">
+        <v>207</v>
+      </c>
+      <c r="I25" s="5"/>
+      <c r="J25" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1311,8 +2481,15 @@
         <v>158</v>
       </c>
       <c r="G26" s="4"/>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" t="s">
+        <v>208</v>
+      </c>
+      <c r="I26" s="5"/>
+      <c r="J26" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -1320,8 +2497,15 @@
         <v>24</v>
       </c>
       <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" t="s">
+        <v>209</v>
+      </c>
+      <c r="I27" s="5"/>
+      <c r="J27" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -1329,8 +2513,15 @@
         <v>25</v>
       </c>
       <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" t="s">
+        <v>210</v>
+      </c>
+      <c r="I28" s="5"/>
+      <c r="J28" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -1338,8 +2529,15 @@
         <v>26</v>
       </c>
       <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" t="s">
+        <v>211</v>
+      </c>
+      <c r="I29" s="5"/>
+      <c r="J29" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -1347,8 +2545,15 @@
         <v>27</v>
       </c>
       <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" t="s">
+        <v>212</v>
+      </c>
+      <c r="I30" s="5"/>
+      <c r="J30" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1356,1043 +2561,1872 @@
         <v>28</v>
       </c>
       <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" t="s">
+        <v>213</v>
+      </c>
+      <c r="I31" s="5"/>
+      <c r="J31" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="H32" t="s">
+        <v>214</v>
+      </c>
+      <c r="I32" s="5"/>
+      <c r="J32" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="H33" t="s">
+        <v>215</v>
+      </c>
+      <c r="I33" s="5"/>
+      <c r="J33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="H34" t="s">
+        <v>216</v>
+      </c>
+      <c r="I34" s="5"/>
+      <c r="J34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="H35" t="s">
+        <v>217</v>
+      </c>
+      <c r="I35" s="5"/>
+      <c r="J35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="H36" t="s">
+        <v>218</v>
+      </c>
+      <c r="I36" s="5"/>
+      <c r="J36" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="H37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I37" s="5"/>
+      <c r="J37" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="H38" t="s">
+        <v>220</v>
+      </c>
+      <c r="I38" s="5"/>
+      <c r="J38" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="H39" t="s">
+        <v>221</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="H40" t="s">
+        <v>222</v>
+      </c>
+      <c r="I40" s="5"/>
+      <c r="J40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="H41" t="s">
+        <v>223</v>
+      </c>
+      <c r="I41" s="5"/>
+      <c r="J41" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="H42" t="s">
+        <v>224</v>
+      </c>
+      <c r="I42" s="5"/>
+      <c r="J42" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="H43" t="s">
+        <v>225</v>
+      </c>
+      <c r="I43" s="5"/>
+      <c r="J43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="H44" t="s">
+        <v>226</v>
+      </c>
+      <c r="I44" s="5"/>
+      <c r="J44" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="H45" t="s">
+        <v>227</v>
+      </c>
+      <c r="I45" s="5"/>
+      <c r="J45" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="H46" t="s">
+        <v>228</v>
+      </c>
+      <c r="I46" s="5"/>
+      <c r="J46" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="H47" t="s">
+        <v>229</v>
+      </c>
+      <c r="I47" s="5"/>
+      <c r="J47" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="H48" t="s">
+        <v>230</v>
+      </c>
+      <c r="I48" s="5"/>
+      <c r="J48" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="H49" t="s">
+        <v>231</v>
+      </c>
+      <c r="I49" s="5"/>
+      <c r="J49" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="H50" t="s">
+        <v>232</v>
+      </c>
+      <c r="I50" s="5"/>
+      <c r="J50" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="H51" t="s">
+        <v>233</v>
+      </c>
+      <c r="I51" s="5"/>
+      <c r="J51" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="H52" t="s">
+        <v>234</v>
+      </c>
+      <c r="I52" s="5"/>
+      <c r="J52" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="H53" t="s">
+        <v>235</v>
+      </c>
+      <c r="I53" s="5"/>
+      <c r="J53" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="H54" t="s">
+        <v>236</v>
+      </c>
+      <c r="I54" s="5"/>
+      <c r="J54" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="H55" t="s">
+        <v>237</v>
+      </c>
+      <c r="I55" s="5"/>
+      <c r="J55" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="H56" t="s">
+        <v>238</v>
+      </c>
+      <c r="I56" s="5"/>
+      <c r="J56" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="H57" t="s">
+        <v>239</v>
+      </c>
+      <c r="I57" s="5"/>
+      <c r="J57" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="H58" t="s">
+        <v>240</v>
+      </c>
+      <c r="I58" s="5"/>
+      <c r="J58" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="H59" t="s">
+        <v>241</v>
+      </c>
+      <c r="I59" s="5"/>
+      <c r="J59" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="H60" t="s">
+        <v>242</v>
+      </c>
+      <c r="I60" s="5"/>
+      <c r="J60" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="H61" t="s">
+        <v>243</v>
+      </c>
+      <c r="I61" s="5"/>
+      <c r="J61" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="H62" t="s">
+        <v>244</v>
+      </c>
+      <c r="J62" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="H63" t="s">
+        <v>245</v>
+      </c>
+      <c r="J63" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="H64" t="s">
+        <v>246</v>
+      </c>
+      <c r="J64" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="H65" t="s">
+        <v>247</v>
+      </c>
+      <c r="J65" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="H66" t="s">
+        <v>248</v>
+      </c>
+      <c r="J66" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="H67" t="s">
+        <v>249</v>
+      </c>
+      <c r="J67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="H68" t="s">
+        <v>250</v>
+      </c>
+      <c r="J68" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="H69" t="s">
+        <v>251</v>
+      </c>
+      <c r="J69" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="H70" t="s">
+        <v>252</v>
+      </c>
+      <c r="J70" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="H71" t="s">
+        <v>253</v>
+      </c>
+      <c r="J71" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="H72" t="s">
+        <v>254</v>
+      </c>
+      <c r="J72" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="H73" t="s">
+        <v>255</v>
+      </c>
+      <c r="J73" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="H74" t="s">
+        <v>256</v>
+      </c>
+      <c r="J74" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="H75" t="s">
+        <v>257</v>
+      </c>
+      <c r="J75" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="H76" t="s">
+        <v>258</v>
+      </c>
+      <c r="J76" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="H77" t="s">
+        <v>259</v>
+      </c>
+      <c r="J77" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="H78" t="s">
+        <v>260</v>
+      </c>
+      <c r="J78" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="H79" t="s">
+        <v>261</v>
+      </c>
+      <c r="J79" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="H80" t="s">
+        <v>262</v>
+      </c>
+      <c r="J80" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="H81" t="s">
+        <v>263</v>
+      </c>
+      <c r="J81" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="H82" t="s">
+        <v>264</v>
+      </c>
+      <c r="J82" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="H83" t="s">
+        <v>265</v>
+      </c>
+      <c r="J83" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="H84" t="s">
+        <v>266</v>
+      </c>
+      <c r="J84" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="H85" t="s">
+        <v>267</v>
+      </c>
+      <c r="J85" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="H86" t="s">
+        <v>268</v>
+      </c>
+      <c r="J86" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="H87" t="s">
+        <v>269</v>
+      </c>
+      <c r="J87" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="H88" t="s">
+        <v>270</v>
+      </c>
+      <c r="J88" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="H89" t="s">
+        <v>271</v>
+      </c>
+      <c r="J89" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="H90" t="s">
+        <v>272</v>
+      </c>
+      <c r="J90" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="H91" t="s">
+        <v>273</v>
+      </c>
+      <c r="J91" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="H92" t="s">
+        <v>274</v>
+      </c>
+      <c r="J92" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="H93" t="s">
+        <v>275</v>
+      </c>
+      <c r="J93" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="H94" t="s">
+        <v>276</v>
+      </c>
+      <c r="J94" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="H95" t="s">
+        <v>277</v>
+      </c>
+      <c r="J95" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="H96" t="s">
+        <v>278</v>
+      </c>
+      <c r="J96" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
+      <c r="H97" t="s">
+        <v>279</v>
+      </c>
+      <c r="J97" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
+      <c r="H98" t="s">
+        <v>280</v>
+      </c>
+      <c r="J98" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
+      <c r="H99" t="s">
+        <v>281</v>
+      </c>
+      <c r="J99" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
       <c r="A100" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
+      <c r="H100" t="s">
+        <v>282</v>
+      </c>
+      <c r="J100" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="102" spans="1:3">
+      <c r="H101" t="s">
+        <v>283</v>
+      </c>
+      <c r="J101" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="103" spans="1:3">
+      <c r="H102" t="s">
+        <v>284</v>
+      </c>
+      <c r="J102" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="104" spans="1:3">
+      <c r="H103" t="s">
+        <v>285</v>
+      </c>
+      <c r="J103" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
       <c r="A104" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="105" spans="1:3">
+      <c r="H104" t="s">
+        <v>286</v>
+      </c>
+      <c r="J104" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
       <c r="A105" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="106" spans="1:3">
+      <c r="H105" t="s">
+        <v>287</v>
+      </c>
+      <c r="J105" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
       <c r="A106" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="107" spans="1:3">
+      <c r="H106" t="s">
+        <v>288</v>
+      </c>
+      <c r="J106" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
       <c r="A107" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="108" spans="1:3">
+      <c r="H107" t="s">
+        <v>289</v>
+      </c>
+      <c r="J107" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
       <c r="A108" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="109" spans="1:3">
+      <c r="H108" t="s">
+        <v>290</v>
+      </c>
+      <c r="J108" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
       <c r="A109" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="110" spans="1:3">
+      <c r="H109" t="s">
+        <v>291</v>
+      </c>
+      <c r="J109" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
       <c r="A110" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="111" spans="1:3">
+      <c r="H110" t="s">
+        <v>292</v>
+      </c>
+      <c r="J110" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
       <c r="A111" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="112" spans="1:3">
+      <c r="H111" t="s">
+        <v>293</v>
+      </c>
+      <c r="J111" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
       <c r="A112" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
+      <c r="H112" t="s">
+        <v>294</v>
+      </c>
+      <c r="J112" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
       <c r="A113" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
+      <c r="H113" t="s">
+        <v>295</v>
+      </c>
+      <c r="J113" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
+      <c r="H114" t="s">
+        <v>296</v>
+      </c>
+      <c r="J114" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
       <c r="A115" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
+      <c r="H115" t="s">
+        <v>297</v>
+      </c>
+      <c r="J115" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
       <c r="A116" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
+      <c r="H116" t="s">
+        <v>298</v>
+      </c>
+      <c r="J116" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
       <c r="A117" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="118" spans="1:3">
+      <c r="H117" t="s">
+        <v>299</v>
+      </c>
+      <c r="J117" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
       <c r="A118" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="119" spans="1:3">
+      <c r="H118" t="s">
+        <v>300</v>
+      </c>
+      <c r="J118" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="A119" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="120" spans="1:3">
+      <c r="H119" t="s">
+        <v>301</v>
+      </c>
+      <c r="J119" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
       <c r="A120" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="121" spans="1:3">
+      <c r="H120" t="s">
+        <v>302</v>
+      </c>
+      <c r="J120" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
       <c r="A121" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="122" spans="1:3">
+      <c r="H121" t="s">
+        <v>303</v>
+      </c>
+      <c r="J121" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
       <c r="A122" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="123" spans="1:3">
+      <c r="H122" t="s">
+        <v>304</v>
+      </c>
+      <c r="J122" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
       <c r="A123" s="1" t="s">
         <v>122</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="124" spans="1:3">
+      <c r="H123" t="s">
+        <v>305</v>
+      </c>
+      <c r="J123" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="A124" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="125" spans="1:3">
+      <c r="H124" t="s">
+        <v>306</v>
+      </c>
+      <c r="J124" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
       <c r="A125" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="126" spans="1:3">
+      <c r="H125" t="s">
+        <v>307</v>
+      </c>
+      <c r="J125" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
       <c r="A126" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="127" spans="1:3">
+      <c r="H126" t="s">
+        <v>308</v>
+      </c>
+      <c r="J126" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
       <c r="A127" s="1" t="s">
         <v>126</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="128" spans="1:3">
+      <c r="H127" t="s">
+        <v>309</v>
+      </c>
+      <c r="J127" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
       <c r="A128" s="1" t="s">
         <v>127</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="129" spans="1:3">
+      <c r="H128" t="s">
+        <v>310</v>
+      </c>
+      <c r="J128" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
       <c r="A129" s="1" t="s">
         <v>128</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="130" spans="1:3">
+      <c r="H129" t="s">
+        <v>311</v>
+      </c>
+      <c r="J129" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
       <c r="A130" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
+      <c r="H130" t="s">
+        <v>312</v>
+      </c>
+      <c r="J130" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
       <c r="A131" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="132" spans="1:3">
+      <c r="H131" t="s">
+        <v>313</v>
+      </c>
+      <c r="J131" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
       <c r="A132" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="133" spans="1:3">
+      <c r="H132" t="s">
+        <v>314</v>
+      </c>
+      <c r="J132" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
       <c r="A133" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="134" spans="1:3">
+      <c r="H133" t="s">
+        <v>315</v>
+      </c>
+      <c r="J133" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
       <c r="A134" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="135" spans="1:3">
+      <c r="H134" t="s">
+        <v>316</v>
+      </c>
+      <c r="J134" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
       <c r="A135" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
+      <c r="H135" t="s">
+        <v>317</v>
+      </c>
+      <c r="J135" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
       <c r="A136" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="137" spans="1:3">
+      <c r="H136" t="s">
+        <v>318</v>
+      </c>
+      <c r="J136" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
       <c r="A137" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="138" spans="1:3">
+      <c r="H137" t="s">
+        <v>319</v>
+      </c>
+      <c r="J137" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
       <c r="A138" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="139" spans="1:3">
+      <c r="H138" t="s">
+        <v>320</v>
+      </c>
+      <c r="J138" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
       <c r="A139" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="140" spans="1:3">
+      <c r="H139" t="s">
+        <v>321</v>
+      </c>
+      <c r="J139" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
       <c r="A140" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="141" spans="1:3">
+      <c r="H140" t="s">
+        <v>322</v>
+      </c>
+      <c r="J140" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
       <c r="A141" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="142" spans="1:3">
+      <c r="H141" t="s">
+        <v>323</v>
+      </c>
+      <c r="J141" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
       <c r="A142" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="143" spans="1:3">
+      <c r="H142" t="s">
+        <v>324</v>
+      </c>
+      <c r="J142" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
       <c r="A143" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="144" spans="1:3">
+      <c r="H143" t="s">
+        <v>325</v>
+      </c>
+      <c r="J143" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
       <c r="A144" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="145" spans="1:3">
+      <c r="H144" t="s">
+        <v>326</v>
+      </c>
+      <c r="J144" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
       <c r="A145" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="146" spans="1:3">
+      <c r="H145" t="s">
+        <v>327</v>
+      </c>
+      <c r="J145" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
       <c r="A146" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="147" spans="1:3">
+      <c r="H146" t="s">
+        <v>328</v>
+      </c>
+      <c r="J146" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
       <c r="A147" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="148" spans="1:3">
+      <c r="H147" t="s">
+        <v>329</v>
+      </c>
+      <c r="J147" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
       <c r="A148" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="149" spans="1:3">
+      <c r="H148" t="s">
+        <v>330</v>
+      </c>
+      <c r="J148" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
       <c r="A149" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="150" spans="1:3">
+      <c r="H149" t="s">
+        <v>331</v>
+      </c>
+      <c r="J149" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
       <c r="A150" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="151" spans="1:3">
+      <c r="H150" t="s">
+        <v>332</v>
+      </c>
+      <c r="J150" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
       <c r="A151" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="152" spans="1:3">
+      <c r="H151" t="s">
+        <v>333</v>
+      </c>
+      <c r="J151" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
       <c r="A152" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="153" spans="1:3">
+      <c r="H152" t="s">
+        <v>334</v>
+      </c>
+      <c r="J152" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
       <c r="A153" s="1" t="s">
         <v>152</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="154" spans="1:3">
+      <c r="H153" t="s">
+        <v>335</v>
+      </c>
+      <c r="J153" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
       <c r="A154" s="1" t="s">
         <v>153</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="155" spans="1:3">
+      <c r="H154" t="s">
+        <v>336</v>
+      </c>
+      <c r="J154" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
       <c r="A155" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="156" spans="1:3">
+      <c r="H155" t="s">
+        <v>337</v>
+      </c>
+      <c r="J155" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
       <c r="A156" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="157" spans="1:3">
+      <c r="H156" t="s">
+        <v>338</v>
+      </c>
+      <c r="J156" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
       <c r="A157" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="158" spans="1:3">
+      <c r="H157" t="s">
+        <v>339</v>
+      </c>
+      <c r="J157" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
       <c r="C158" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="159" spans="1:3">
+      <c r="H158" t="s">
+        <v>340</v>
+      </c>
+      <c r="J158" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
       <c r="C159" s="2" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="160" spans="1:3">
+      <c r="H159" t="s">
+        <v>341</v>
+      </c>
+      <c r="J159" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
       <c r="C160" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="161" spans="3:3">
+      <c r="H160" t="s">
+        <v>342</v>
+      </c>
+      <c r="J160" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="161" spans="3:10">
       <c r="C161" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="162" spans="3:3">
+      <c r="H161" t="s">
+        <v>343</v>
+      </c>
+      <c r="J161" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="162" spans="3:10">
       <c r="C162" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="163" spans="3:3">
+      <c r="H162" t="s">
+        <v>344</v>
+      </c>
+      <c r="J162" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="163" spans="3:10">
       <c r="C163" s="3" t="s">
         <v>156</v>
+      </c>
+      <c r="H163" t="s">
+        <v>345</v>
+      </c>
+      <c r="J163" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
